--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T12:12:39+00:00</t>
+    <t>2024-11-05T09:00:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:00:17+00:00</t>
+    <t>2024-11-05T09:16:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:16:22+00:00</t>
+    <t>2024-11-05T10:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T10:26:22+00:00</t>
+    <t>2024-11-06T09:40:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2601" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="483">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T09:40:37+00:00</t>
+    <t>2024-11-07T06:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,21 +431,21 @@
     <t>Encounter.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -455,43 +455,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Encounter.extension:altersgruppe</t>
-  </si>
-  <si>
-    <t>altersgruppe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-altersgruppe}
-</t>
-  </si>
-  <si>
-    <t>Altersgruppe</t>
-  </si>
-  <si>
-    <t>Nach dem Alter in Gruppen eingeteilt, wobei vollendete Lebensjahre ausschlaggebend sind.</t>
-  </si>
-  <si>
-    <t>Encounter.extension:neugeborenes</t>
-  </si>
-  <si>
-    <t>neugeborenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-neugeborenes}
-</t>
-  </si>
-  <si>
-    <t>Neugeborenes</t>
-  </si>
-  <si>
-    <t>Ein Patient wird als Neugeborenes bezeichnet, wenn das Alter zum Zugangszeitpunkt auf die Abteilung &lt;28 Tage ist.</t>
-  </si>
-  <si>
     <t>Encounter.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -499,9 +463,6 @@
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
@@ -873,9 +834,6 @@
   </si>
   <si>
     <t>Encounter.participant.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1360,6 +1318,36 @@
   </si>
   <si>
     <t>Encounter.admission.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Encounter.admission.extension:Altersgruppe</t>
+  </si>
+  <si>
+    <t>Altersgruppe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-altersgruppe}
+</t>
+  </si>
+  <si>
+    <t>In Gruppen eingeteilt, wobei vollendete Lebensjahre ausschlaggebend sind.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}moped-inv-Altersgruppe-1:If 'neugeborenes' is true then 'beiZugang' must be age group 0. {$this.extension('neugeborenes') = true implies $this.extension('beiZugang') = '0'}</t>
   </si>
   <si>
     <t>Encounter.admission.modifierExtension</t>
@@ -1857,12 +1845,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN72"/>
+  <dimension ref="A1:AN71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.58984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.3125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.58984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.19921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.8984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2826,7 +2814,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2845,15 +2833,17 @@
         <v>19</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>19</v>
@@ -2890,14 +2880,16 @@
         <v>19</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>139</v>
@@ -2921,7 +2913,7 @@
         <v>19</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>19</v>
@@ -2932,41 +2924,43 @@
         <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>19</v>
       </c>
@@ -3014,7 +3008,7 @@
         <v>19</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -3035,7 +3029,7 @@
         <v>19</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>19</v>
@@ -3046,11 +3040,9 @@
         <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>19</v>
       </c>
@@ -3059,7 +3051,7 @@
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>19</v>
@@ -3068,16 +3060,16 @@
         <v>19</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3128,7 +3120,7 @@
         <v>19</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3140,38 +3132,38 @@
         <v>19</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>19</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>19</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>19</v>
@@ -3183,20 +3175,18 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>19</v>
       </c>
@@ -3220,13 +3210,13 @@
         <v>19</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>19</v>
@@ -3244,39 +3234,39 @@
         <v>19</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>19</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3299,13 +3289,13 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3332,13 +3322,13 @@
         <v>19</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>19</v>
@@ -3356,7 +3346,7 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3371,24 +3361,24 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3396,7 +3386,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>87</v>
@@ -3405,23 +3395,21 @@
         <v>19</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>19</v>
@@ -3446,13 +3434,13 @@
         <v>19</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>19</v>
@@ -3470,10 +3458,10 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>87</v>
@@ -3485,24 +3473,24 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>19</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3525,15 +3513,17 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>19</v>
@@ -3558,31 +3548,31 @@
         <v>19</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="Z15" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3597,24 +3587,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>19</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3625,7 +3615,7 @@
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>19</v>
@@ -3634,16 +3624,16 @@
         <v>19</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3670,13 +3660,13 @@
         <v>19</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
@@ -3694,13 +3684,13 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>19</v>
@@ -3709,35 +3699,35 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>19</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
+        <v>19</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>19</v>
+        <v>201</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>19</v>
@@ -3749,16 +3739,16 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3784,13 +3774,13 @@
         <v>19</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>19</v>
@@ -3808,13 +3798,13 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>19</v>
@@ -3823,24 +3813,24 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3851,7 +3841,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>19</v>
@@ -3860,18 +3850,20 @@
         <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>19</v>
@@ -3896,13 +3888,11 @@
         <v>19</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>19</v>
@@ -3920,13 +3910,13 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>19</v>
@@ -3935,35 +3925,35 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>200</v>
+        <v>19</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>210</v>
+        <v>19</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>213</v>
+        <v>19</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>19</v>
@@ -3975,17 +3965,15 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>19</v>
@@ -4034,13 +4022,13 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>19</v>
@@ -4049,35 +4037,35 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>218</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>19</v>
@@ -4089,17 +4077,15 @@
         <v>19</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>177</v>
+        <v>223</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N20" t="s" s="2">
         <v>225</v>
       </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>19</v>
@@ -4124,11 +4110,13 @@
         <v>19</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>19</v>
@@ -4146,13 +4134,13 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>19</v>
@@ -4161,13 +4149,13 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>19</v>
+        <v>226</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>19</v>
+        <v>227</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>19</v>
@@ -4175,10 +4163,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4198,16 +4186,16 @@
         <v>19</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4258,7 +4246,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4276,32 +4264,32 @@
         <v>19</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>232</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>19</v>
@@ -4313,15 +4301,17 @@
         <v>19</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M22" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>19</v>
@@ -4370,13 +4360,13 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>19</v>
@@ -4385,13 +4375,13 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>19</v>
@@ -4399,10 +4389,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4413,7 +4403,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>19</v>
@@ -4425,13 +4415,13 @@
         <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4482,13 +4472,13 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>19</v>
@@ -4497,24 +4487,24 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>19</v>
+        <v>243</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4525,7 +4515,7 @@
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>19</v>
@@ -4534,19 +4524,19 @@
         <v>19</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4596,39 +4586,39 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>19</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4651,13 +4641,13 @@
         <v>19</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4708,7 +4698,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4717,34 +4707,34 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>255</v>
+        <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>256</v>
+        <v>198</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4760,19 +4750,19 @@
         <v>19</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>135</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>136</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>262</v>
+        <v>138</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4822,7 +4812,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4834,59 +4824,63 @@
         <v>19</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>263</v>
+        <v>140</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>265</v>
+        <v>198</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>266</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>268</v>
+        <v>135</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
       </c>
@@ -4934,19 +4928,19 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>272</v>
+        <v>19</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>19</v>
@@ -4955,7 +4949,7 @@
         <v>19</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>19</v>
@@ -4963,14 +4957,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4986,19 +4980,19 @@
         <v>19</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>155</v>
+        <v>272</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5024,13 +5018,13 @@
         <v>19</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>19</v>
+        <v>273</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>19</v>
+        <v>271</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>19</v>
@@ -5048,7 +5042,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5057,66 +5051,62 @@
         <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>19</v>
+        <v>276</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>19</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>278</v>
+        <v>19</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>280</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>19</v>
       </c>
@@ -5164,19 +5154,19 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>19</v>
@@ -5185,18 +5175,18 @@
         <v>19</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>132</v>
+        <v>283</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>19</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5207,7 +5197,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>19</v>
@@ -5219,16 +5209,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>177</v>
+        <v>286</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5254,13 +5244,13 @@
         <v>19</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>284</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>19</v>
@@ -5278,39 +5268,39 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>19</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5321,7 +5311,7 @@
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>19</v>
@@ -5330,16 +5320,16 @@
         <v>19</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5390,13 +5380,13 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>19</v>
@@ -5405,24 +5395,24 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>19</v>
+        <v>226</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5433,7 +5423,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>19</v>
@@ -5442,19 +5432,19 @@
         <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5504,39 +5494,39 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>255</v>
+        <v>19</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>303</v>
+        <v>19</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>304</v>
+        <v>132</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>305</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5547,7 +5537,7 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>19</v>
@@ -5556,18 +5546,20 @@
         <v>19</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -5616,13 +5608,13 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>19</v>
@@ -5631,10 +5623,10 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>238</v>
+        <v>308</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>19</v>
+        <v>309</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>310</v>
@@ -5659,7 +5651,7 @@
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>19</v>
@@ -5679,9 +5671,7 @@
       <c r="M34" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N34" t="s" s="2">
-        <v>316</v>
-      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -5736,7 +5726,7 @@
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>19</v>
@@ -5751,10 +5741,10 @@
         <v>19</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>19</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35">
@@ -5785,7 +5775,7 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>318</v>
@@ -5793,9 +5783,7 @@
       <c r="M35" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>320</v>
-      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>19</v>
@@ -5859,24 +5847,24 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>321</v>
+        <v>19</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>322</v>
+        <v>19</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>323</v>
+        <v>19</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5899,15 +5887,17 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -5956,7 +5946,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5971,24 +5961,24 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>19</v>
+        <v>326</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5999,7 +5989,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>19</v>
@@ -6008,18 +5998,20 @@
         <v>19</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>326</v>
+        <v>247</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6068,13 +6060,13 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>19</v>
@@ -6092,15 +6084,15 @@
         <v>19</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>333</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6123,17 +6115,15 @@
         <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>335</v>
+        <v>256</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>336</v>
+        <v>257</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>19</v>
@@ -6182,7 +6172,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>259</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6191,34 +6181,34 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>321</v>
+        <v>19</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>339</v>
+        <v>198</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>340</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6234,19 +6224,19 @@
         <v>19</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>259</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>342</v>
+        <v>136</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>343</v>
+        <v>262</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>344</v>
+        <v>138</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6296,7 +6286,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>263</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6308,7 +6298,7 @@
         <v>19</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>19</v>
@@ -6317,7 +6307,7 @@
         <v>19</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>19</v>
@@ -6325,42 +6315,46 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>268</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>19</v>
       </c>
@@ -6408,19 +6402,19 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>272</v>
+        <v>19</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>19</v>
@@ -6429,7 +6423,7 @@
         <v>19</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>19</v>
@@ -6437,14 +6431,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6460,20 +6454,18 @@
         <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>274</v>
+        <v>336</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -6498,13 +6490,11 @@
         <v>19</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>19</v>
+        <v>338</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>19</v>
@@ -6522,7 +6512,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6534,7 +6524,7 @@
         <v>19</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>19</v>
@@ -6543,7 +6533,7 @@
         <v>19</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>210</v>
+        <v>19</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>19</v>
@@ -6551,14 +6541,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>278</v>
+        <v>340</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6571,26 +6561,22 @@
         <v>19</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>341</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>279</v>
+        <v>342</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>19</v>
       </c>
@@ -6614,13 +6600,13 @@
         <v>19</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>19</v>
+        <v>344</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>19</v>
+        <v>345</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>19</v>
@@ -6638,7 +6624,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>281</v>
+        <v>339</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6650,27 +6636,27 @@
         <v>19</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>19</v>
+        <v>346</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>19</v>
+        <v>347</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>132</v>
+        <v>348</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>19</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6693,15 +6679,17 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -6726,11 +6714,13 @@
         <v>19</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>351</v>
+        <v>19</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>19</v>
@@ -6748,7 +6738,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6769,7 +6759,7 @@
         <v>19</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>19</v>
+        <v>354</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>19</v>
@@ -6777,21 +6767,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>353</v>
+        <v>19</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>19</v>
@@ -6800,16 +6790,16 @@
         <v>19</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>354</v>
+        <v>256</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>355</v>
+        <v>257</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
+        <v>258</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6836,13 +6826,13 @@
         <v>19</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>357</v>
+        <v>19</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>19</v>
@@ -6860,43 +6850,43 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>352</v>
+        <v>259</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>359</v>
+        <v>19</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>361</v>
+        <v>198</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6912,19 +6902,19 @@
         <v>19</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>259</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>364</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>365</v>
+        <v>262</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>366</v>
+        <v>138</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6974,7 +6964,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>363</v>
+        <v>263</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6986,7 +6976,7 @@
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>19</v>
@@ -6995,7 +6985,7 @@
         <v>19</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>367</v>
+        <v>198</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>19</v>
@@ -7003,42 +6993,46 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>268</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>19</v>
       </c>
@@ -7086,19 +7080,19 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>272</v>
+        <v>19</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>19</v>
@@ -7107,7 +7101,7 @@
         <v>19</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>19</v>
@@ -7115,14 +7109,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>152</v>
+        <v>359</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7138,20 +7132,18 @@
         <v>19</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>360</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>274</v>
+        <v>361</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -7176,13 +7168,11 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>19</v>
@@ -7200,7 +7190,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>276</v>
+        <v>358</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7212,31 +7202,31 @@
         <v>19</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>19</v>
+        <v>346</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>19</v>
+        <v>347</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>210</v>
+        <v>364</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>19</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>278</v>
+        <v>19</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7249,26 +7239,22 @@
         <v>19</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>279</v>
+        <v>367</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>19</v>
       </c>
@@ -7292,13 +7278,13 @@
         <v>19</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>19</v>
+        <v>369</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>19</v>
+        <v>370</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>19</v>
@@ -7316,7 +7302,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>281</v>
+        <v>366</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7328,7 +7314,7 @@
         <v>19</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>19</v>
@@ -7337,22 +7323,22 @@
         <v>19</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>19</v>
+        <v>371</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>372</v>
+        <v>19</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7368,7 +7354,7 @@
         <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>373</v>
@@ -7379,7 +7365,9 @@
       <c r="M49" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N49" s="2"/>
+      <c r="N49" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7404,11 +7392,13 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>376</v>
+        <v>19</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
@@ -7426,7 +7416,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7441,24 +7431,24 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>359</v>
+        <v>19</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>377</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>378</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7481,16 +7471,20 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
       </c>
@@ -7514,13 +7508,13 @@
         <v>19</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>19</v>
@@ -7538,7 +7532,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7559,18 +7553,18 @@
         <v>19</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>210</v>
+        <v>385</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7593,17 +7587,15 @@
         <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>386</v>
+        <v>165</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N51" t="s" s="2">
         <v>389</v>
       </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -7628,13 +7620,13 @@
         <v>19</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>19</v>
+        <v>390</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>19</v>
+        <v>391</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>19</v>
@@ -7652,7 +7644,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7673,18 +7665,18 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>19</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7707,20 +7699,18 @@
         <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>19</v>
       </c>
@@ -7744,13 +7734,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -7768,7 +7758,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7789,18 +7779,18 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7811,7 +7801,7 @@
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>19</v>
@@ -7823,15 +7813,17 @@
         <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -7856,13 +7848,13 @@
         <v>19</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>403</v>
+        <v>19</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>404</v>
+        <v>19</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>19</v>
@@ -7880,13 +7872,13 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>19</v>
@@ -7901,10 +7893,10 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>406</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
@@ -7923,7 +7915,7 @@
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>19</v>
@@ -7935,17 +7927,15 @@
         <v>19</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>177</v>
+        <v>256</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>408</v>
+        <v>257</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -7970,13 +7960,13 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>411</v>
+        <v>19</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>412</v>
+        <v>19</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>19</v>
@@ -7994,19 +7984,19 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>407</v>
+        <v>259</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>19</v>
@@ -8015,18 +8005,18 @@
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>413</v>
+        <v>198</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>414</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8037,7 +8027,7 @@
         <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>19</v>
@@ -8049,17 +8039,15 @@
         <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>259</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>19</v>
@@ -8096,31 +8084,29 @@
         <v>19</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>19</v>
+        <v>412</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>415</v>
+        <v>263</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>19</v>
@@ -8129,7 +8115,7 @@
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>419</v>
+        <v>19</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>19</v>
@@ -8137,12 +8123,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>19</v>
       </c>
@@ -8163,13 +8151,13 @@
         <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>268</v>
+        <v>415</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>269</v>
+        <v>414</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>270</v>
+        <v>416</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8220,19 +8208,19 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>272</v>
+        <v>19</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>19</v>
+        <v>417</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>19</v>
@@ -8241,7 +8229,7 @@
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>210</v>
+        <v>19</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>19</v>
@@ -8249,14 +8237,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>152</v>
+        <v>265</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8269,24 +8257,26 @@
         <v>19</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>19</v>
       </c>
@@ -8334,7 +8324,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8355,7 +8345,7 @@
         <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>19</v>
@@ -8363,46 +8353,42 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>278</v>
+        <v>19</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>279</v>
+        <v>420</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>19</v>
       </c>
@@ -8450,19 +8436,19 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>281</v>
+        <v>419</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>19</v>
@@ -8471,10 +8457,10 @@
         <v>19</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>19</v>
+        <v>422</v>
       </c>
     </row>
     <row r="59">
@@ -8505,13 +8491,13 @@
         <v>19</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>159</v>
+        <v>424</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8583,18 +8569,18 @@
         <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>164</v>
+        <v>427</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>426</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8617,7 +8603,7 @@
         <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>428</v>
+        <v>165</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>429</v>
@@ -8650,13 +8636,13 @@
         <v>19</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>19</v>
+        <v>431</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>19</v>
+        <v>432</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>19</v>
@@ -8674,7 +8660,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8695,18 +8681,18 @@
         <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>19</v>
+        <v>434</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8729,13 +8715,13 @@
         <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8762,31 +8748,31 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8807,18 +8793,18 @@
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>437</v>
+        <v>198</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8841,13 +8827,13 @@
         <v>19</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>177</v>
+        <v>424</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8874,13 +8860,13 @@
         <v>19</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>442</v>
+        <v>19</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>443</v>
+        <v>19</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>19</v>
@@ -8898,7 +8884,7 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8919,18 +8905,18 @@
         <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>210</v>
+        <v>444</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8953,13 +8939,13 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>428</v>
+        <v>165</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8986,13 +8972,11 @@
         <v>19</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>19</v>
+        <v>449</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>19</v>
@@ -9010,7 +8994,7 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9031,18 +9015,18 @@
         <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9053,7 +9037,7 @@
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>19</v>
@@ -9065,15 +9049,17 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>19</v>
@@ -9098,11 +9084,13 @@
         <v>19</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>453</v>
+        <v>19</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>19</v>
@@ -9120,13 +9108,13 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>19</v>
@@ -9141,18 +9129,18 @@
         <v>19</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>455</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9163,7 +9151,7 @@
         <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>19</v>
@@ -9175,17 +9163,15 @@
         <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>457</v>
+        <v>257</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -9234,19 +9220,19 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>456</v>
+        <v>259</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>19</v>
@@ -9255,7 +9241,7 @@
         <v>19</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>460</v>
+        <v>198</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>19</v>
@@ -9263,21 +9249,21 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>19</v>
@@ -9289,15 +9275,17 @@
         <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>268</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>19</v>
@@ -9346,19 +9334,19 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>272</v>
+        <v>19</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>19</v>
@@ -9367,7 +9355,7 @@
         <v>19</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>19</v>
@@ -9375,14 +9363,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>152</v>
+        <v>265</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9395,24 +9383,26 @@
         <v>19</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>19</v>
       </c>
@@ -9460,7 +9450,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9481,7 +9471,7 @@
         <v>19</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>19</v>
@@ -9489,46 +9479,42 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>278</v>
+        <v>19</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>134</v>
+        <v>461</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>279</v>
+        <v>462</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>19</v>
       </c>
@@ -9576,39 +9562,39 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>281</v>
+        <v>460</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>19</v>
+        <v>464</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>19</v>
+        <v>465</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>132</v>
+        <v>291</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>19</v>
+        <v>466</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9616,7 +9602,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>87</v>
@@ -9631,15 +9617,17 @@
         <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>465</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>19</v>
@@ -9664,13 +9652,13 @@
         <v>19</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>19</v>
+        <v>471</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>19</v>
+        <v>472</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>19</v>
@@ -9688,10 +9676,10 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>87</v>
@@ -9703,24 +9691,24 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>468</v>
+        <v>19</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>469</v>
+        <v>19</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>304</v>
+        <v>473</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>470</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9743,16 +9731,16 @@
         <v>19</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9778,13 +9766,13 @@
         <v>19</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>19</v>
@@ -9802,7 +9790,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9823,7 +9811,7 @@
         <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>477</v>
+        <v>19</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>19</v>
@@ -9831,10 +9819,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9857,17 +9845,15 @@
         <v>19</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>177</v>
+        <v>280</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -9892,13 +9878,13 @@
         <v>19</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>482</v>
+        <v>19</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>483</v>
+        <v>19</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>19</v>
@@ -9916,7 +9902,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9937,121 +9923,9 @@
         <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>19</v>
+        <v>283</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AN72" t="s" s="2">
         <v>19</v>
       </c>
     </row>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T06:21:30+00:00</t>
+    <t>2024-11-07T13:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T13:12:32+00:00</t>
+    <t>2024-11-07T14:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T14:31:26+00:00</t>
+    <t>2024-11-08T06:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:16:09+00:00</t>
+    <t>2024-11-12T07:45:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
